--- a/forms/trg/Formulir_TRG_prg.xlsx
+++ b/forms/trg/Formulir_TRG_prg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. rer. nat. Ir. AM Imran Oemar</t>
+          <t>Prof. Dr. Eng. Ir. Meutia Farida, ST., MT.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Carbonate Sedimentology, Quaternary Geology, Disaster Management</t>
+          <t>Micropaleontology, Stratigraphy, Paleoceanography</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,7 +933,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>56507213000</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sultan, ST., MT</t>
+          <t>Prof. Dr. rer. nat. Ir. AM Imran Oemar</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Geophysics, Geohydrology, Oceanography</t>
+          <t>Carbonate Sedimentology, Quaternary Geology, Disaster Management</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +987,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sc. Muhammad Sulhuzair, ST., MT.</t>
+          <t>Dr. Sultan, ST., MT</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Organic Geochemistry, Petroleum Geology, Paleoenvironment</t>
+          <t>Geophysics, Geohydrology, Oceanography</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Safruddim, ST., M.Eng.</t>
+          <t>Dr. Sc. Muhammad Sulhuzair, ST., MT.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Sedimentology, Economic Mineral, Geochemistry</t>
+          <t>Organic Geochemistry, Petroleum Geology, Paleoenvironment</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,20 +1061,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Shun Chiyonobu</t>
+          <t>Safruddim, ST., M.Eng.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Akita University Japan</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n"/>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Sedimentology, Economic Mineral, Geochemistry</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1094,12 +1098,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Makoto Yamasaki</t>
+          <t>Prof. Dr. Shun Chiyonobu</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1127,24 +1131,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>George Bernard Ngomano</t>
+          <t>Dr. Makoto Yamasaki</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Akita University</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Petroleum Geochemistry</t>
-        </is>
-      </c>
+          <t>Akita University Japan</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1164,18 +1164,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sc. Renaldi Suhendra, ST., M.Sc.</t>
+          <t>George Bernard Ngomano</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Akita University</t>
+        </is>
+      </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>BRIN</t>
+          <t>Petroleum Geochemistry</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1197,18 +1201,18 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Ir. Jimmi Nugraha, ST., MT</t>
+          <t>Dr. Sc. Renaldi Suhendra, ST., M.Sc.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>BMKG</t>
+          <t>BRIN</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1230,20 +1234,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Tirta Nian Febrianti</t>
+          <t>Ir. Jimmi Nugraha, ST., MT</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>BMKG</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1263,12 +1267,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Nurul Ilmi Abdullah</t>
+          <t>Tirta Nian Febrianti</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1296,12 +1300,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Rahmatul Sarfat</t>
+          <t>Nurul Ilmi Abdullah</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1329,12 +1333,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Savira Aulia R.</t>
+          <t>Muhammad Rahmatul Sarfat</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1362,12 +1366,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>M. Al Izza Hizbullah</t>
+          <t>Savira Aulia R.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1395,12 +1399,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Tati Fitriana</t>
+          <t>M. Al Izza Hizbullah</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1408,11 +1412,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>PRG Team</t>
-        </is>
-      </c>
+      <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1430,10 +1430,26 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Tati Fitriana</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>PRG Team</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1441,7 +1457,11 @@
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1630,15 +1650,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
